--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Lo que NO se toca" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Caja Chica — análisis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cómo se midió" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Caja Chica — el dinero" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Caja Chica — personas" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +73,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF9999"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -89,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +114,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1023,126 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CAJAS CHICAS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar o reasignar 2 cajas VIGENTES de gente dada de baja</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2 cajas, $20,000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CCH 250 a nombre de ANA ITZEL PEREZ LOPEZ, dada de baja el 01/11/2023 (hace casi 3 años), con $10,000. Y CCH 254 de JOCELYN ALVAREZ FRANCO, baja el 21/09/2026, con $10,000. Las dos siguen en ESTATUS=VIGENTE.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Dos fondos activos de $10,000 cada uno a nombre de personas que ya no trabajan aquí. De todo lo que salió hoy, esto es lo más urgente.</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>URGENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CAJAS CHICAS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Corregir el encabezado JEFE INMEDIATO DEL REPSONSABLE</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1 encabezado</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Dice REPSONSABLE en vez de RESPONSABLE. Es una columna real y con datos (223 de 285).</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Cualquier código que la busque por nombre tiene que escribir el error a propósito, y el que la escriba bien no la encuentra.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ARQUEOS</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Que el sistema nuevo CALCULE los totales en vez de recibirlos</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2 columnas</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>En la hoja no hay una sola fórmula: TOTAL GENERAL y DIFERENCIA son números literales que escribió AppSheet. Por eso hoy pueden no cuadrar con el desglose (ver la hoja 'Caja Chica — el dinero').</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mientras los totales se reciban ya calculados, DIFERENCIA puede valer 0 sin que eso signifique que la caja cuadró. Si el sistema nuevo los deriva del desglose, la inconsistencia se vuelve imposible.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1020,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1297,6 +1431,33 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>145 de 145</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ARQUEOS — DIFERENCIA = 0 en 84 arqueos</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Parece que nadie revisa nada porque siempre cuadra</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Un arqueo sano se ve exactamente así: el total contado igual al fondo autorizado. El problema NO es que valga 0, es que TOTAL GENERAL se recibe ya calculado y no se puede comprobar. Ver la hoja 'Caja Chica — el dinero'.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84 de 145</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1615,6 +1776,527 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Lo que NO se midió (actualizado)</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Ya se midieron las dos cosas que faltaban de Caja Chica: los datos de persona contra COLABORADORES y la aritmética de los arqueos. Queda pendiente de Líneas la distribución de los cambios en el tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Un límite que hay que saber</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>ARQUEOS no tiene fórmulas: todos sus totales son valores literales que escribió AppSheet. Eso significa que el spreadsheet NO permite verificar de dónde sale TOTAL GENERAL. Cualquier conclusión sobre eso tiene que venir del área.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Qué se midió</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas M 0,50 … B 1000,00: ¿piezas o importes?</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PIEZAS, 145 de 145</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Probé las dos hipótesis. Sumadas tal cual cuadran 123 y 111 veces; multiplicadas por su denominación cuadran 145 y 145. Son conteos de piezas, sin excepción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL M = suma de monedas x denominación</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL B = suma de billetes x denominación</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL EFECTIVO = TOTAL M + TOTAL B</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto. La parte de efectivo de la hoja es internamente consistente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>¿Hay fórmulas en la hoja?</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Todos los valores son literales escritos por AppSheet: TOTAL GENERAL = 15000, DIFERENCIA = 0, sin fórmula detrás. Por eso la hoja no se puede auto-verificar, y por eso no puedo saber de dónde sale TOTAL GENERAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Arqueos SIN efectivo contado (TOTAL EFECTIVO = 0)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>109 de 145</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>En 3 de cada 4 arqueos no se capturó ni una moneda ni un billete. Puede ser que no hubiera efectivo, o que no se capture el desglose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL == MONTO CAJA exactamente</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>100 de 145</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Cuando eso pasa, DIFERENCIA sale 0 por aritmética. Un arqueo sano se ve así, así que NO es en sí una señal mala.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL contra la suma de sus 11 columnas</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>no cuadra en 111 de 145</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>La brecha suma $986,185.11. Ejemplo extremo: el arqueo 2026_219_002, caja de $50,000, todas las columnas de desglose en 0.00, y TOTAL GENERAL = $50,000.60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>LO QUE ESTO SÍ DICE, Y LO QUE NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Lo que NO se puede concluir</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Que falte dinero. No hay evidencia de eso, y hay explicaciones inocentes: que el efectivo estuviera ahí pero no se capturara el desglose por denominación, o que el detalle de comprobantes viva en el PDF del arqueo y estas 11 columnas sean un resumen parcial. Ninguna de las dos se puede descartar desde el spreadsheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lo que SÍ dice</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Que la hoja no reconcilia consigo misma en 111 de 145 arqueos, y que DIFERENCIA = 0 no es prueba de que la caja cuadró: es la resta de dos números que alguien más calculó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>La pregunta exacta para el área</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Cuando TOTAL EFECTIVO = 0 y TOTAL GENERAL = 15,000: ¿es que no se contó el efectivo, o que no había efectivo y todo estaba en comprobantes? Si es lo segundo, los comprobantes deberían sumar 15,000 y suman 3,650.89. Con esa respuesta se sabe si la brecha es natural o no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>El arreglo que sí está en nuestras manos</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Que el sistema nuevo CALCULE TOTAL EFECTIVO, TOTAL GENERAL y DIFERENCIA a partir del desglose, en vez de recibirlos ya hechos. Así la inconsistencia se vuelve imposible, sin importar cuál sea la respuesta de arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>De paso, dos columnas que se vuelven innecesarias</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>CANTIDAD M y CANTIDAD B están vacías en los 145 arqueos, y son justo la suma de piezas que el sistema nuevo podría calcular solo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Columna en CAJAS CHICAS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contra COLABORADORES ACTUALIZADO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Coinciden</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Difieren</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>% de acuerdo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSABLE DE CAJA CHICA</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRE COMPLETO</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Sobre todo acentos y nombres compuestos. La persona es la correcta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mismo nivel que en Líneas. Sincronizable con revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>JEFE INMEDIATO DEL REPSONSABLE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>JEFE DIRECTO</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Y 62 sin dato de un lado. Flojo para sincronizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OFICINA</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>OFICINA/DESARROLLO</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Muy bajo. Probablemente miden cosas distintas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SEDE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SEDE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>El MISMO 26% que en Líneas. Dos familias distintas dan el mismo número, así que no es coincidencia: la sede de la caja y la sede donde trabaja la persona son cosas distintas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PUESTO DE RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>PUESTO</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>232</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>El más bajo de todo el sistema. No sincronizar sin preguntar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Cómo se emparejó</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CAJAS CHICAS no tiene número de empleado. Se emparejó por CORREO ELECTRONICO DE RESPONSABLE (216 de 285, 76%) y por nombre (277, 97%); con cualquiera de las dos, 283 de 285 (99%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Lo bueno</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>El 99% de las cajas encuentran a su responsable en el catálogo. Es la tasa más alta de las tres familias: en Líneas es 45%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Lo que NO se debe sincronizar</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>PUESTO (17%), SEDE (26%) y OFICINA (28%). Que SEDE dé exactamente el mismo 26% que en Líneas refuerza que esa columna significa algo distinto del catálogo de personas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Lo que NO se toca" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Caja Chica — análisis" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Cómo se midió" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Caja Chica — el dinero" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Caja Chica — personas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Caja Chica — personas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Caja Chica — el dinero" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +78,11 @@
         <fgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -123,6 +128,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1119,7 +1128,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Que el sistema nuevo CALCULE los totales en vez de recibirlos</t>
+          <t>Que el sistema nuevo derive los totales, por robustez</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1129,12 +1138,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>En la hoja no hay una sola fórmula: TOTAL GENERAL y DIFERENCIA son números literales que escribió AppSheet. Por eso hoy pueden no cuadrar con el desglose (ver la hoja 'Caja Chica — el dinero').</t>
+          <t>ARQUEOS cuadra al centavo en los 145 (ver 'Caja Chica — el dinero'), así que esto YA NO es un defecto. Pero en la hoja no hay una sola fórmula: TOTAL GENERAL y DIFERENCIA son literales que escribió AppSheet. Nada impide que un día lleguen mal.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Mientras los totales se reciban ya calculados, DIFERENCIA puede valer 0 sin que eso signifique que la caja cuadró. Si el sistema nuevo los deriva del desglose, la inconsistencia se vuelve imposible.</t>
+          <t>Nada roto hoy. Es una mejora: si el sistema nuevo los calcula desde el desglose, la inconsistencia se vuelve imposible en vez de depender de que quien escriba lo haga bien.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1154,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1452,12 +1461,39 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Un arqueo sano se ve exactamente así: el total contado igual al fondo autorizado. El problema NO es que valga 0, es que TOTAL GENERAL se recibe ya calculado y no se puede comprobar. Ver la hoja 'Caja Chica — el dinero'.</t>
+          <t>Un arqueo sano se ve exactamente así, y DIFERENCIA SÍ es un control real: TOTAL GENERAL cuadra con sus 12 partes en los 145 arqueos. Una versión anterior de este archivo decía que el total no se podía comprobar; era un error de medición mío.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>84 de 145</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ARQUEOS — TOTAL EFECTIVO = 0 en 109 arqueos</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Un arqueo sin una sola moneda ni billete contado</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>El fondo de esas cajas no es efectivo: está en cuenta bancaria o fintech, y se registra en DISPONIBLE CUENTA BANCARIA (111 arqueos, $986,185.11). La hoja incluso tiene DESCRIPCION CUENTA BANCARIA y Nombre_Fintech.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>109 de 145</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1796,7 +1832,19 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>ARQUEOS no tiene fórmulas: todos sus totales son valores literales que escribió AppSheet. Eso significa que el spreadsheet NO permite verificar de dónde sale TOTAL GENERAL. Cualquier conclusión sobre eso tiene que venir del área.</t>
+          <t>ARQUEOS no tiene fórmulas: sus totales son valores literales que escribió AppSheet. Eso NO impide verificarlos —cuadran los 145— pero sí significa que la fórmula vive en AppSheet y no en el spreadsheet. La que aplica la confirmó Ayrton el 30/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Una corrección de este archivo</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>La primera versión reportó una brecha de $986,185.11 en TOTAL GENERAL. Estaba mal: sumé 11 de las 12 columnas de la fórmula y omití DISPONIBLE CUENTA BANCARIA, que suma exactamente esa cantidad. ARQUEOS cuadra al centavo en los 145 arqueos. Queda anotado para que nadie persiga un problema que no existe.</t>
         </is>
       </c>
     </row>
@@ -1806,245 +1854,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Qué se midió</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Lectura</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Las columnas M 0,50 … B 1000,00: ¿piezas o importes?</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>PIEZAS, 145 de 145</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Probé las dos hipótesis. Sumadas tal cual cuadran 123 y 111 veces; multiplicadas por su denominación cuadran 145 y 145. Son conteos de piezas, sin excepción.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL M = suma de monedas x denominación</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>145 de 145</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Perfecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL B = suma de billetes x denominación</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>145 de 145</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Perfecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL EFECTIVO = TOTAL M + TOTAL B</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>145 de 145</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Perfecto. La parte de efectivo de la hoja es internamente consistente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>¿Hay fórmulas en la hoja?</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>NINGUNA</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Todos los valores son literales escritos por AppSheet: TOTAL GENERAL = 15000, DIFERENCIA = 0, sin fórmula detrás. Por eso la hoja no se puede auto-verificar, y por eso no puedo saber de dónde sale TOTAL GENERAL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Arqueos SIN efectivo contado (TOTAL EFECTIVO = 0)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>109 de 145</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>En 3 de cada 4 arqueos no se capturó ni una moneda ni un billete. Puede ser que no hubiera efectivo, o que no se capture el desglose.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL GENERAL == MONTO CAJA exactamente</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>100 de 145</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Cuando eso pasa, DIFERENCIA sale 0 por aritmética. Un arqueo sano se ve así, así que NO es en sí una señal mala.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL GENERAL contra la suma de sus 11 columnas</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>no cuadra en 111 de 145</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>La brecha suma $986,185.11. Ejemplo extremo: el arqueo 2026_219_002, caja de $50,000, todas las columnas de desglose en 0.00, y TOTAL GENERAL = $50,000.60.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>LO QUE ESTO SÍ DICE, Y LO QUE NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Lo que NO se puede concluir</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Que falte dinero. No hay evidencia de eso, y hay explicaciones inocentes: que el efectivo estuviera ahí pero no se capturara el desglose por denominación, o que el detalle de comprobantes viva en el PDF del arqueo y estas 11 columnas sean un resumen parcial. Ninguna de las dos se puede descartar desde el spreadsheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Lo que SÍ dice</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Que la hoja no reconcilia consigo misma en 111 de 145 arqueos, y que DIFERENCIA = 0 no es prueba de que la caja cuadró: es la resta de dos números que alguien más calculó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>La pregunta exacta para el área</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Cuando TOTAL EFECTIVO = 0 y TOTAL GENERAL = 15,000: ¿es que no se contó el efectivo, o que no había efectivo y todo estaba en comprobantes? Si es lo segundo, los comprobantes deberían sumar 15,000 y suman 3,650.89. Con esa respuesta se sabe si la brecha es natural o no.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>El arreglo que sí está en nuestras manos</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Que el sistema nuevo CALCULE TOTAL EFECTIVO, TOTAL GENERAL y DIFERENCIA a partir del desglose, en vez de recibirlos ya hechos. Así la inconsistencia se vuelve imposible, sin importar cuál sea la respuesta de arriba.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>De paso, dos columnas que se vuelven innecesarias</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>CANTIDAD M y CANTIDAD B están vacías en los 145 arqueos, y son justo la suma de piezas que el sistema nuevo podría calcular solo.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2300,4 +2109,214 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Qué se midió</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Lectura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas M 0,50 … B 1000,00: ¿piezas o importes?</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>PIEZAS, 145 de 145</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Probé las dos hipótesis. Sumadas tal cual cuadran 123 y 111 veces; multiplicadas por su denominación cuadran 145 y 145. Son conteos de piezas, sin excepción.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL M = suma de monedas × denominación</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL B = suma de billetes × denominación</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL EFECTIVO = TOTAL M + TOTAL B</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>145 de 145</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Perfecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL = la suma de sus 12 partes</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>145 de 145  ✓</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Cuadra al centavo en los 145 arqueos, con brecha total de $0.00. La fórmula, que Ayrton verificó en AppSheet el 30/09/2026, es: TOTAL EFECTIVO + DISPONIBLE CUENTA BANCARIA + TOTAL CHEQUES + los 8 de facturas y viáticos + OTROS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DIFERENCIA = TOTAL GENERAL − MONTO CAJA</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>144 de 145</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>La única excepción es el arqueo 2026_222_001, con el signo invertido: dice −2.50 y debería ser +2.50. Es la limpieza #12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Arqueos sin efectivo físico (TOTAL EFECTIVO = 0)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>109 de 145</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>NO es un hallazgo: el fondo de esas cajas está en una CUENTA BANCARIA, no en efectivo. DISPONIBLE CUENTA BANCARIA trae dato en 111 de los 145 arqueos y suma $986,185.11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>CORRECCIÓN A UNA VERSIÓN ANTERIOR DE ESTA HOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Qué decía</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Que TOTAL GENERAL no cuadraba con sus partes en 111 de 145 arqueos, con una brecha acumulada de $986,185.11 «sin explicar».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Por qué estaba mal</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Sumé 11 columnas y la fórmula tiene 12: me faltó DISPONIBLE CUENTA BANCARIA. Esa columna suma exactamente $986,185.11 — el mismo número, al centavo. La brecha era mi omisión, no un problema de los datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lo que en realidad pasa</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Muchas cajas no guardan efectivo: su fondo está en una cuenta bancaria o fintech (la hoja tiene DESCRIPCION CUENTA BANCARIA y Nombre_Fintech). Por eso TOTAL EFECTIVO = 0 en 109 arqueos, y es normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Y sobre DIFERENCIA = 0</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>También estaba mal dicho. Con la fórmula completa, DIFERENCIA sí es un control real: compara el total de lo que hay contra el fondo autorizado. Que valga 0 significa que la caja cuadró, no que el número esté inventado.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1152,6 +1152,46 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CAJAS CHICAS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Agregar la llave de la PERSONA responsable</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1 columna, 283 filas</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Es la unica referencia que falta en la familia: CAJAS CHICAS no tiene No EMPLEADO, solo el nombre y el correo. Se puede rellenar: 283 de 285 (99%) emparejan con COLABORADORES ACTUALIZADO por correo (76%) o por nombre (97%).</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Sin ella no hay forma automatica de saber que una caja VIGENTE esta a nombre de alguien dado de baja. Las dos de la limpieza #13 se encontraron a mano.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1163,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1494,6 +1534,33 @@
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>109 de 145</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Caja Chica</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ARQUEOS — sus columnas copiadas del catalogo</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>MONTO CAJA no coincide con el catalogo en 4 arqueos</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ARQUEOS es una BITACORA y sus copias estan al 97-100%: RESPONSABLE 145/145, AREA / DEPARTAMENTO 145/145, METODO REEMBOLSO 145/145, PUESTO 144/145. Los 4 MONTO CAJA distintos estan explicados los 4 por INCREMENTOS: el arqueo guardo el fondo de ESE dia y el catalogo muestra el de hoy. Sincronizar destruiria 4 registros correctos para arreglar 0 problemas.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4 de 145</t>
         </is>
       </c>
     </row>

--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +83,11 @@
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E2E2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,6 +137,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,7 +706,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDO, TERCER, CUARTO y QUINTO RESPONSABLE, cada uno con su NOMBRE y PUESTO: 0 filas con dato en las 15. Solo se usan RESPONSABLE (100%) y NOMBRE QUIEN USA (11%).</t>
+          <t>SEGUNDO, TERCER, CUARTO y QUINTO RESPONSABLE, cada uno con su NOMBRE y PUESTO: 0 filas con dato en las 15. Solo se usan RESPONSABLE (100%) y NOMBRE QUIEN USA (11%). || 30/09/2026: hay que volver a medirlo. LINEAS TELEFONICAS paso de 56 a 58 columnas en la reestructuracion, asi que el juego de columnas vacias cambio.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +716,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>EN PAUSA</t>
+          <t>RE-MEDIR</t>
         </is>
       </c>
     </row>
@@ -738,7 +746,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Entre PUESTO QUINTO RESPONSABLE y PUESTO RESPONSABLES 2. En el libro de pruebas alguien ya la reparó como NOMBRE RESPONSABLES 2; en producción sigue rota.</t>
+          <t>Entre PUESTO QUINTO RESPONSABLE y PUESTO RESPONSABLES 2. En el libro de pruebas alguien ya la reparó como NOMBRE RESPONSABLES 2; en producción sigue rota. || 30/09/2026: YA ESTA HECHO. Emmanuel la reparo en el libro compartido: ahora se llama NOMBRE RESPONSABLES 2. Falta aplicarlo en produccion.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -746,9 +754,9 @@
           <t>Una columna sin nombre usable, y el error se arrastra a cualquier copia del libro.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>EN PAUSA</t>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>HECHO</t>
         </is>
       </c>
     </row>
@@ -778,7 +786,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>NUMERO TELEFONO='NO APLICA' en 638 filas (son equipos SIN línea) e IMEI con 'N/A' x25, 'TELCEL' x10, '0' x6, 'SOLO LINEA' x3, 'NA' x2.</t>
+          <t>NUMERO TELEFONO='NO APLICA' en 638 filas (son equipos SIN línea) e IMEI con 'N/A' x25, 'TELCEL' x10, '0' x6, 'SOLO LINEA' x3, 'NA' x2. || 30/09/2026: sigue valiendo. LINEAS TELEFONICAS no se elimino, y NUCO sigue siendo llave unica (1,615 de 1,615) despues de la reestructuracion.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +826,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Esas 3 hojas NO tienen ningún vínculo con la línea: su FOLIO es un consecutivo propio (1, 2, 3, 4…). Por cascada emparejan: Desecho 228/228 (100%), Solicitud 206/229 (90%), Reactivación 301/361 (83%). El IMEI va primero porque nunca cambia y no tiene duplicados.</t>
+          <t>Esas 3 hojas NO tienen ningún vínculo con la línea: su FOLIO es un consecutivo propio (1, 2, 3, 4…). Por cascada emparejan: Desecho 228/228 (100%), Solicitud 206/229 (90%), Reactivación 301/361 (83%). El IMEI va primero porque nunca cambia y no tiene duplicados. || 30/09/2026: YA NO APLICA. Las tres hojas -REACTIVACION DE LINEAS, SOLICITUD DE LINEAS y BITACORA DE DESECHO- se ELIMINARON en la reestructuracion de Lineas. No implementar la cascada.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -826,9 +834,9 @@
           <t>Tres hojas huérfanas del padre. No se puede saber qué línea se reactivó ni qué equipo se desechó sin cruzar a mano.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>EN PAUSA</t>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>YA NO APLICA</t>
         </is>
       </c>
     </row>
@@ -858,7 +866,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Ese ID no existe en la hoja madre y le apuntan 3 inspecciones, 4 responsivas y 18 cambios.</t>
+          <t>Ese ID no existe en la hoja madre y le apuntan 3 inspecciones, 4 responsivas y 18 cambios. || 30/09/2026: hay que volver a medirlo. Las hijas perdieron filas -CAMBIOS LINEAS TELEFONICAS -1,961, INSPECCIONES LINEAS -170, RESPONSIVAS LINEAS -133- asi que los 25 hijos huerfanos de EEBA06A3 ya no son 25.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -868,7 +876,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>EN PAUSA</t>
+          <t>RE-MEDIR</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1920,18 @@
       <c r="B12" s="9" t="inlineStr">
         <is>
           <t>La primera versión reportó una brecha de $986,185.11 en TOTAL GENERAL. Estaba mal: sumé 11 de las 12 columnas de la fórmula y omití DISPONIBLE CUENTA BANCARIA, que suma exactamente esa cantidad. ARQUEOS cuadra al centavo en los 145 arqueos. Queda anotado para que nadie persiga un problema que no existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lineas se reestructuro el 30/09/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Hubo junta del area y los cambios ya estan en el libro COMPARTIDO del equipo (1fC77Uu1...), no en produccion. Se eliminaron 4 pestañas: HISTORIAL_REASIGNACIONES, REACTIVACION DE LINEAS, SOLICITUD DE LINEAS y BITACORA DE DESECHO. Por eso las limpiezas 5, 7, 4 y 8 cambiaron de estado. Verificado despues de la reestructuracion: NUCO sigue siendo llave unica, 1,615 de 1,615. Detalle en docs/lineas-homologacion.md, en el aviso de arriba.</t>
         </is>
       </c>
     </row>

--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1195,6 +1195,90 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>HOLOGRAMAS</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Quitar el guión bajo inicial de 13 series de SERIE VEHICULO</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13 celdas</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13 series traen un '_' de más al inicio ('_VR3EC9HP2MJ503983'). Sin ese carácter, la serie SÍ existe en VEHICULOS: son el mismo vehículo, escrito mal. Es la limpieza más barata y más segura de toda la lista, porque el padre se comprueba antes de tocar nada.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13 hologramas se quedan sin ID VEHICULO para siempre, contados como 'vehículo personal' cuando sí están en el catálogo. La tasa de HOLOGRAMAS queda en 56% en vez de 62%, y el número engaña a quien lo lea después.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>HOLOGRAMAS</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Revisar 7 valores de SERIE VEHICULO que no tienen forma de VIN</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>7 celdas</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Un VIN tiene 17 caracteres. Estos no: '1', '123456789', 'UYC383A' (parece una placa, no una serie), '1GNM616030' (10), 'L15A77804197' (12) y '3MDDJBTVXKM31054' (16, le falta uno). Los dos últimos se ven como dedazo recuperable; los primeros, como relleno.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Quedan 7 hologramas que nunca van a emparejar con nada y que ensucian la cuenta de vehículos personales. No rompen nada, pero tampoco se pueden auditar.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -1310,22 +1394,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HOLOGRAMAS — 111 filas sin vehículo</t>
+          <t>HOLOGRAMAS — 91 filas sin vehículo</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>44% no empareja con el catálogo</t>
+          <t>36% no empareja con el catálogo</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Son vehículos PERSONALES que por diseño no están en el catálogo, y ahí los datos se capturan a mano. Está documentado en docs/relaciones.md.</t>
+          <t>Son vehículos PERSONALES que por diseño no están en el catálogo, y ahí los datos se capturan a mano. CORRECCIÓN (30/09/2026): antes decían 111. Al medirlas después de escribir ID VEHICULO resultó que 13 traen un '_' de más y 7 no tienen forma de VIN — esas 20 SÍ se limpian, y son las limpiezas #17 y #18. Personales de verdad son 91.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111 filas</t>
+          <t>91 filas (antes decía 111)</t>
         </is>
       </c>
     </row>

--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -31,17 +31,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -70,6 +67,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
@@ -78,18 +85,8 @@
         <fgColor rgb="00FF9999"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E2E2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -97,47 +94,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -505,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -754,7 +741,7 @@
           <t>Una columna sin nombre usable, y el error se arrastra a cualquier copia del libro.</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>HECHO</t>
         </is>
@@ -834,7 +821,7 @@
           <t>Tres hojas huérfanas del padre. No se puede saber qué línea se reactivó ni qué equipo se desechó sin cruzar a mano.</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>YA NO APLICA</t>
         </is>
@@ -914,7 +901,7 @@
           <t>Una columna que promete un dato y nunca lo da.</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>DECISION DE NEGOCIO</t>
         </is>
@@ -1074,7 +1061,7 @@
           <t>Dos fondos activos de $10,000 cada uno a nombre de personas que ya no trabajan aquí. De todo lo que salió hoy, esto es lo más urgente.</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>URGENTE</t>
         </is>
@@ -1281,6 +1268,166 @@
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Vaciar SERIE SENSOR de los 22 vehículos cuyo sensor está en BAJA</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22 celdas</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Al dar de baja un sensor nadie limpiaba VEHICULOS. Medido en producción el 01/10/2026: los 22 son reales (los mismos en el libro del equipo), no datos de prueba. Decisión de Ayrton (01/10/2026): al dar de baja, se vacía. Desde ahora INSTALACION DE SENSORES es la dueña de SERIE SENSOR y SENSOR en VEHICULOS (al revés de las demás columnas, donde VEHICULOS es la dueña).</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS sigue mostrando como instalada la serie de un sensor que ya se retiró.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Vaciar SERIE SENSOR de CTA0295 y CTA0481: tienen serie pero ningún renglón de sensor</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2 celdas</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Sus series (G95Z0ZTP77A1 y G9W5HX33RZ6H) no aparecen en INSTALACION DE SENSORES. CAVEAT: puede ser un sensor instalado que nunca se registró. Si es así, lo correcto es DAR DE ALTA el sensor, no borrar la serie. Revisarlos antes de sincronizar: la pantalla de Relaciones los lista uno por uno.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Una serie que no se puede rastrear a ninguna instalación ni responsiva.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Reducir SENSOR a dos valores: SI TIENE SENSOR / NO TIENE SENSOR</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>39 celdas</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Decisión de Ayrton (01/10/2026). Se calcula del sensor: ACTIVO → SI TIENE; en BAJA o sin renglón → NO TIENE. Pasan a NO TIENE 36: CANCELADO 18, SENSOR TI 5, NO COMPATIBLE 2, NO APLICA AUTO DG 2, EN PROCESO DE INSTALACION 1, vacío 2, y 6 que dicen SI TIENE sin sensor activo. Pasan a SI TIENE 3 con sensor activo (CANCELADO 2, SENSOR TI 1). CAVEAT: se PIERDE el matiz de CANCELADO, NO COMPATIBLE, SENSOR TI, etc. — si hace falta, tendrá que vivir en otra columna. Y los 6 "SI TIENE" sin activo pueden ser sensores no registrados, igual que la limpieza #20.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>SENSOR dice una cosa y la hoja de sensores otra en 39 vehículos, y nadie sabe cuál creer.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS / HOLOGRAMAS / INSPECCION VEHICULAR</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Medir y decidir el dueño de 3 columnas que se llaman igual en VEHICULOS y en una hija</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3 columnas</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Aparecieron al revisar Sensores y NO están en el mapa de Relaciones: HOLOGRAMAS.NO ECONOMICO (no se sabe quién manda), INSPECCION VEHICULAR.POLIZA SEGURO (probablemente la póliza del día: bitácora) y VEHICULOS.VERIFICACION (SI / NO) (huele a resumen de VERIFICACIONES, como SENSOR).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Pueden estar desincronizadas sin que nada lo detecte, igual que SERIE SENSOR hasta hoy.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>RE-MEDIR</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1800,60 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>4 de 145</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>INSTALACION DE SENSORES.TIPO DE COMBUSTIBLE y HOLOGRAMAS.RAZON SOCIAL</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Se llaman igual que una columna de VEHICULOS, así que parecen copias desincronizadas</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Significan otra cosa. En Sensores es el PRODUCTO que carga la unidad (MAGNA/PREMIUM/DIESEL) y en VEHICULOS el tipo de motor (GASOLINA/DIESEL); en Hologramas es la empresa del contrato de la tarjeta, no la dueña del vehículo. Por eso NO están en el mapa de Relaciones y nunca se sincronizan.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2 columnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>INSTALACION DE SENSORES → VEHICULOS: un solo renglón de sensor por vehículo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Una sincronización "simple" podría tener que escoger entre varios sensores de la misma unidad</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hoy no hace falta escoger: en producción cada vehículo tiene a lo más un renglón de sensor (208 de 208). Es una SUPOSICIÓN medida, no una regla del sistema: si algún día una unidad tiene dos renglones (una reinstalación), la sincronización lo reporta como llave repetida y NO toca VEHICULOS hasta que alguien lo resuelva.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208 de 208</t>
         </is>
       </c>
     </row>
@@ -1856,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1876,7 +2077,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
@@ -1888,7 +2089,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Libro</t>
         </is>
@@ -1900,7 +2101,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Acceso</t>
         </is>
@@ -1912,7 +2113,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Método</t>
         </is>
@@ -1924,7 +2125,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Ojo con las lecturas truncadas</t>
         </is>
@@ -1936,7 +2137,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Documentos relacionados</t>
         </is>
@@ -1948,7 +2149,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Lo que NO se midió</t>
         </is>
@@ -1960,7 +2161,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Estado de Líneas</t>
         </is>
@@ -1971,51 +2172,63 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Lo que NO se midió (actualizado)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Ya se midieron las dos cosas que faltaban de Caja Chica: los datos de persona contra COLABORADORES y la aritmética de los arqueos. Queda pendiente de Líneas la distribución de los cambios en el tiempo.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Un límite que hay que saber</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>ARQUEOS no tiene fórmulas: sus totales son valores literales que escribió AppSheet. Eso NO impide verificarlos —cuadran los 145— pero sí significa que la fórmula vive en AppSheet y no en el spreadsheet. La que aplica la confirmó Ayrton el 30/09/2026.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Una corrección de este archivo</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>La primera versión reportó una brecha de $986,185.11 en TOTAL GENERAL. Estaba mal: sumé 11 de las 12 columnas de la fórmula y omití DISPONIBLE CUENTA BANCARIA, que suma exactamente esa cantidad. ARQUEOS cuadra al centavo en los 145 arqueos. Queda anotado para que nadie persiga un problema que no existe.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Lineas se reestructuro el 30/09/2026</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Hubo junta del area y los cambios ya estan en el libro COMPARTIDO del equipo (1fC77Uu1...), no en produccion. Se eliminaron 4 pestañas: HISTORIAL_REASIGNACIONES, REACTIVACION DE LINEAS, SOLICITUD DE LINEAS y BITACORA DE DESECHO. Por eso las limpiezas 5, 7, 4 y 8 cambiaron de estado. Verificado despues de la reestructuracion: NUCO sigue siendo llave unica, 1,615 de 1,615. Detalle en docs/lineas-homologacion.md, en el aviso de arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Sensores ↔ VEHICULOS (01/10/2026)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Medido en PRODUCCIÓN (1h5ibDsmVtrG27rwMaOvj-lm08QZUHzDv3woPmkfRQrk), solo lectura. Producción no tiene la columna ID, así que ahí se emparejó por SERIE VEHICULO, igual que Relaciones.gs. Resultado: 648 vehículos y 208 renglones de sensor (186 ACTIVO, 22 BAJA), con a lo más UN renglón por vehículo (208 de 208). En el libro del equipo salen además 3 casos que son datos de prueba y no existen en producción: la serie 'prueba', AUT0025 con dos sensores activos y una serie activa en otro vehículo.</t>
         </is>
       </c>
     </row>
@@ -2241,41 +2454,53 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Cómo se emparejó</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>CAJAS CHICAS no tiene número de empleado. Se emparejó por CORREO ELECTRONICO DE RESPONSABLE (216 de 285, 76%) y por nombre (277, 97%); con cualquiera de las dos, 283 de 285 (99%).</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Lo bueno</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>El 99% de las cajas encuentran a su responsable en el catálogo. Es la tasa más alta de las tres familias: en Líneas es 45%.</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Lo que NO se debe sincronizar</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>PUESTO (17%), SEDE (26%) y OFICINA (28%). Que SEDE dé exactamente el mismo 26% que en Líneas refuerza que esa columna significa algo distinto del catálogo de personas.</t>
         </is>
       </c>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2319,7 +2544,7 @@
           <t>Las columnas M 0,50 … B 1000,00: ¿piezas o importes?</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>PIEZAS, 145 de 145</t>
         </is>
@@ -2336,7 +2561,7 @@
           <t>TOTAL M = suma de monedas × denominación</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>145 de 145</t>
         </is>
@@ -2353,7 +2578,7 @@
           <t>TOTAL B = suma de billetes × denominación</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>145 de 145</t>
         </is>
@@ -2370,7 +2595,7 @@
           <t>TOTAL EFECTIVO = TOTAL M + TOTAL B</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>145 de 145</t>
         </is>
@@ -2387,7 +2612,7 @@
           <t>TOTAL GENERAL = la suma de sus 12 partes</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>145 de 145  ✓</t>
         </is>
@@ -2404,7 +2629,7 @@
           <t>DIFERENCIA = TOTAL GENERAL − MONTO CAJA</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>144 de 145</t>
         </is>
@@ -2421,7 +2646,7 @@
           <t>Arqueos sin efectivo físico (TOTAL EFECTIVO = 0)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>109 de 145</t>
         </is>
@@ -2433,55 +2658,61 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>CORRECCIÓN A UNA VERSIÓN ANTERIOR DE ESTA HOJA</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Qué decía</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Que TOTAL GENERAL no cuadraba con sus partes en 111 de 145 arqueos, con una brecha acumulada de $986,185.11 «sin explicar».</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Por qué estaba mal</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Sumé 11 columnas y la fórmula tiene 12: me faltó DISPONIBLE CUENTA BANCARIA. Esa columna suma exactamente $986,185.11 — el mismo número, al centavo. La brecha era mi omisión, no un problema de los datos.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Lo que en realidad pasa</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Muchas cajas no guardan efectivo: su fondo está en una cuenta bancaria o fintech (la hoja tiene DESCRIPCION CUENTA BANCARIA y Nombre_Fintech). Por eso TOTAL EFECTIVO = 0 en 109 arqueos, y es normal.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>Y sobre DIFERENCIA = 0</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>También estaba mal dicho. Con la fórmula completa, DIFERENCIA sí es un control real: compara el total de lo que hay contra el fondo autorizado. Que valga 0 significa que la caja cuadró, no que el número esté inventado.</t>
         </is>

--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Cómo se midió" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Caja Chica — personas" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Caja Chica — el dinero" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Nombres de columnas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1432,46 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Homologar el nombre de la columna UBICACION → OFICINA / DESARROLLO</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1 encabezado</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Es el mismo dato que INSTALACION DE SENSORES, INSPECCION VEHICULAR, las hojas de Líneas y los catálogos (LISTAS, DEPARTAMENTOS) llaman OFICINA / DESARROLLO; VEHICULOS era la única que le decía UBICACION, y sus opciones ya salían del catálogo OFICINA / DESARROLLO. Decisión de Ayrton (01/10/2026): homologar los nombres en toda la base, caso por caso — ver la pestaña "Nombres de columnas". Lo hace el paso "nombres" del pipeline de Vehículos (vehiculos2Escribir).</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>El mismo dato con dos nombres: la pantalla Datos conectados tiene que explicar "en Sensores se llama…", y cualquier cruce entre hojas tiene que saber la equivalencia.</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1442,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1854,6 +1895,33 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>208 de 208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CAMBIOS VEHICULOS — renglones con CAMPO = UBICACION</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Después de la limpieza #23 la columna ya no se llama así</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Es el historial: dice cómo se llamaba la columna cuando se hizo el cambio, y reescribirlo falsearía el registro. Consecuencia que hay que saber: desde el renombre, los cambios nuevos de ese dato se anotan como OFICINA / DESARROLLO, así que su historial queda con DOS nombres. Quien filtre Cambios Vehículos por ese dato tiene que buscar los dos.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>489 en producción (467 en el libro del equipo)</t>
         </is>
       </c>
     </row>
@@ -2721,4 +2789,121 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Familia</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hoja</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Se llama hoy</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Se va a llamar</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Así se llama en</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Por qué ese nombre</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Qué cambia junto</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Vehículos</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>VEHICULOS</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>UBICACION</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>OFICINA / DESARROLLO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>INSTALACION DE SENSORES, INSPECCION VEHICULAR, LINEAS TELEFONICAS y sus hijas, LISTAS, DEPARTAMENTOS</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que usa el resto de la base, y la única hoja distinta era la dueña del dato. Renombrar una columna es más barato que renombrar cinco.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>En el mismo commit: Relaciones.MAPA, InspeccionesService.DEL_VEHICULO y el formulario de Vehículos (la etiqueta para la gente sigue siendo "Ubicación"). AppSheet: en producción ya estará apagado cuando corra el pipeline; en el libro del equipo, la app de pruebas de AppSheet deja de ver la columna hasta regenerar su esquema. El historial de CAMBIOS VEHICULOS no se toca (ver "Lo que NO se toca").</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/limpiezas-planeadas.xlsx
+++ b/limpiezas-planeadas.xlsx
@@ -2797,7 +2797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2903,6 +2903,241 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Líneas</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>INSPECCIONES LINEAS, RESPONSIVAS LINEAS</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No TELEFONO</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>NUMERO TELEFONO</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>LINEAS TELEFONICAS</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que tiene en la hoja dueña (LINEAS TELEFONICAS). Medido el 01/10/2026 uniendo por ID LINEA: 74% y 85% iguales; las diferencias son la línea de hoy contra la del día del documento.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Es código de Líneas (Emmanuel): LineasCaptura, LineasRepo y los formularios de inspección y responsiva buscan estas columnas por nombre. Decidir con él antes de agregarlas a MIGRACION_NOMBRES.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>POR DECIDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Líneas</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>INSPECCIONES LINEAS, RESPONSIVAS LINEAS</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>NUMERO SIM</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>LINEAS TELEFONICAS</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que tiene en la hoja dueña (LINEAS TELEFONICAS). Medido el 01/10/2026 uniendo por ID LINEA: 84% y 93% iguales.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Es código de Líneas (Emmanuel): LineasCaptura, LineasRepo y los formularios de inspección y responsiva buscan estas columnas por nombre. Decidir con él antes de agregarlas a MIGRACION_NOMBRES.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>POR DECIDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Líneas</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>INSPECCIONES LINEAS, RESPONSIVAS LINEAS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>CUENTA GOOGLE</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>LINEAS TELEFONICAS</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que tiene en la hoja dueña (LINEAS TELEFONICAS). Medido el 01/10/2026 uniendo por ID LINEA: 53% y 68% iguales, y el bot ACTUALIZAR DESDE INSPECCION ya las trata como la misma columna.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Es código de Líneas (Emmanuel): LineasCaptura, LineasRepo y los formularios de inspección y responsiva buscan estas columnas por nombre. Decidir con él antes de agregarlas a MIGRACION_NOMBRES.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>POR DECIDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Líneas</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>INSPECCIONES LINEAS, RESPONSIVAS LINEAS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>LINEAS TELEFONICAS</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que tiene en la hoja dueña (LINEAS TELEFONICAS). Medido el 01/10/2026 uniendo por ID LINEA: 99.7% y 99.3% iguales.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Es código de Líneas (Emmanuel): LineasCaptura, LineasRepo y los formularios de inspección y responsiva buscan estas columnas por nombre. Decidir con él antes de agregarlas a MIGRACION_NOMBRES.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>POR DECIDIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Líneas</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSIVAS LINEAS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>No EMPLEADO</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NO EMPLEADO</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>LINEAS TELEFONICAS</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Es el nombre que tiene en la hoja dueña (LINEAS TELEFONICAS). Medido el 01/10/2026 uniendo por ID LINEA: 66% iguales; solo cambian las mayúsculas, que para el código ya son dos columnas distintas.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Es código de Líneas (Emmanuel): LineasCaptura, LineasRepo y los formularios de inspección y responsiva buscan estas columnas por nombre. Decidir con él antes de agregarlas a MIGRACION_NOMBRES.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>POR DECIDIR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
